--- a/outputs/Заявка на весь ассортимент.xlsx
+++ b/outputs/Заявка на весь ассортимент.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I174"/>
+  <dimension ref="A1:I210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1633,16 +1633,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>8809480652165</t>
+          <t>8809755462123</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
+          <t>ENOUGH - Collagen 3in1 Sun Cream</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F46" s="5" t="n"/>
       <c r="G46" s="5" t="n"/>
@@ -1658,14 +1658,18 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>8809347960303</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
+          <t>ENOUGH - Collagen Hydro Moisture Two way Cake 13 тон</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F47" s="5" t="n"/>
       <c r="G47" s="5" t="n"/>
@@ -1683,12 +1687,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>8809605872263</t>
+          <t>8809347960310</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+          <t>ENOUGH - Collagen Hydro Moisture Two way Cake 21 тон</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
@@ -1710,16 +1714,16 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>8809605872270</t>
+          <t>8809480652165</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F49" s="5" t="n"/>
       <c r="G49" s="5" t="n"/>
@@ -1735,18 +1739,14 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>8809605872287</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+          <t>ENOUGH - Collagen Moisture Sun Cream</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F50" s="5" t="n"/>
       <c r="G50" s="5" t="n"/>
@@ -1762,18 +1762,14 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>8809474498809</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ENOUGH Gold snail moisture foundation #13</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F51" s="5" t="n"/>
       <c r="G51" s="5" t="n"/>
@@ -1791,16 +1787,16 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>8809474498816</t>
+          <t>8809480652097</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ENOUGH Gold snail moisture foundation #21</t>
+          <t>ENOUGH - Collagen Whitening Moisture Two Way Cake 13 тон</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F52" s="5" t="n"/>
       <c r="G52" s="5" t="n"/>
@@ -1818,12 +1814,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8809605871938</t>
+          <t>8809480652103</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ENOUGH Premium Rich Gold Double Wear Radiance Foundation #13</t>
+          <t>ENOUGH - Collagen Whitening Moisture Two Way Cake 21 тон</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
@@ -1845,16 +1841,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8809605871945</t>
+          <t>8809605872263</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ENOUGH Premium Rich Gold Double Wear Radiance Foundation #21</t>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F54" s="5" t="n"/>
       <c r="G54" s="5" t="n"/>
@@ -1872,16 +1868,16 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>8809605870993</t>
+          <t>8809605872270</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ENOUGH Premium Ultra X10 cover up Collagen foundation #13</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F55" s="5" t="n"/>
       <c r="G55" s="5" t="n"/>
@@ -1889,41 +1885,53 @@
       <c r="I55" s="5" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>ETUDE</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
+      <c r="A56" t="n">
+        <v>50</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>8809605872287</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8809668028041</t>
+          <t>8809474498809</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [160ml] / Пенка с содой для глубокого очищения и снятия макияжа</t>
+          <t>ENOUGH Gold snail moisture foundation #13</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F57" s="5" t="n"/>
       <c r="G57" s="5" t="n"/>
@@ -1932,25 +1940,25 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8809668028058</t>
+          <t>8809474498816</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [30ml] / Пенка с содой для глубокого очищения</t>
+          <t>ENOUGH Gold snail moisture foundation #21</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F58" s="5" t="n"/>
       <c r="G58" s="5" t="n"/>
@@ -1959,25 +1967,25 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>8809820683118</t>
+          <t>8809605871938</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>ENOUGH Premium Rich Gold Double Wear Radiance Foundation #13</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F59" s="5" t="n"/>
       <c r="G59" s="5" t="n"/>
@@ -1986,25 +1994,25 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8809820692707</t>
+          <t>8809605871945</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищающий скраб для лица с содой</t>
+          <t>ENOUGH Premium Rich Gold Double Wear Radiance Foundation #21</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F60" s="5" t="n"/>
       <c r="G60" s="5" t="n"/>
@@ -2013,25 +2021,25 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>8809668028089</t>
+          <t>8809605870993</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Pore Cleansing Foam [160ml] / Пенка для умывания с содой</t>
+          <t>ENOUGH Premium Ultra X10 cover up Collagen foundation #13</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F61" s="5" t="n"/>
       <c r="G61" s="5" t="n"/>
@@ -2039,41 +2047,53 @@
       <c r="I61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="2" t="n"/>
-      <c r="G62" s="2" t="n"/>
-      <c r="H62" s="2" t="n"/>
-      <c r="I62" s="2" t="n"/>
+      <c r="A62" t="n">
+        <v>56</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>8809605871006</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ENOUGH Ultra X10 Cover Up Collagen Foundation 21 тон</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>8809595053659</t>
+          <t>8809605871013</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
+          <t>ENOUGH Ultra X10 Cover Up Collagen Foundation 23 тон</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F63" s="5" t="n"/>
       <c r="G63" s="5" t="n"/>
@@ -2082,25 +2102,25 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>8809034583617</t>
+          <t>8809438484954</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+          <t>Enough 8 Peptide Sensation Pro Balancing Cream</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F64" s="5" t="n"/>
       <c r="G64" s="5" t="n"/>
@@ -2109,25 +2129,25 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>8800260032009</t>
+          <t>8809726960375</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+          <t>Enough 8 Peptide Sensation Pro Sun Cream</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F65" s="5" t="n"/>
       <c r="G65" s="5" t="n"/>
@@ -2136,25 +2156,25 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>8809317289472</t>
+          <t>8809605870962</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+          <t>Enough 8 Peptide full cover perfect foundation 13 тон</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F66" s="5" t="n"/>
       <c r="G66" s="5" t="n"/>
@@ -2163,21 +2183,21 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>8802221001338</t>
+          <t>8809605870979</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
+          <t>Enough 8 Peptide full cover perfect foundation 21 тон</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
@@ -2190,25 +2210,25 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>8809480772504</t>
+          <t>8809605870986</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+          <t>Enough 8 Peptide full cover perfect foundation 23 тон</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F68" s="5" t="n"/>
       <c r="G68" s="5" t="n"/>
@@ -2217,25 +2237,21 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>8809595053284</t>
-        </is>
-      </c>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
+          <t>Enough Collagen 3X Moisture Cream</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F69" s="5" t="n"/>
       <c r="G69" s="5" t="n"/>
@@ -2244,25 +2260,25 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>8809317289274</t>
+          <t>8809438489584</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+          <t>Enough Collagen 3X Moisture Makeup Fixer</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F70" s="5" t="n"/>
       <c r="G70" s="5" t="n"/>
@@ -2271,25 +2287,25 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>8809480770975</t>
+          <t>8809951050636</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+          <t>Enough Collagen 3X Moisture Stick Foundation SPF50 PA++++ 13N</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F71" s="5" t="n"/>
       <c r="G71" s="5" t="n"/>
@@ -2298,25 +2314,25 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>8809469772778</t>
+          <t>8809951050643</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+          <t>Enough Collagen 3X Moisture Stick Foundation SPF50 PA++++ 21N</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F72" s="5" t="n"/>
       <c r="G72" s="5" t="n"/>
@@ -2324,41 +2340,53 @@
       <c r="I72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n"/>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>HEIMISH</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="2" t="n"/>
-      <c r="G73" s="2" t="n"/>
-      <c r="H73" s="2" t="n"/>
-      <c r="I73" s="2" t="n"/>
+      <c r="A73" t="n">
+        <v>67</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>8809755465285</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Enough Collagen 3X Moisture Sun Cream</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="5" t="n"/>
+      <c r="I73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HEIMISH</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>8809481760463</t>
+          <t>8809541378546</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
+          <t>Enough Collagen 3x Moisture Ampoule</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F74" s="5" t="n"/>
       <c r="G74" s="5" t="n"/>
@@ -2366,41 +2394,53 @@
       <c r="I74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n"/>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="2" t="n"/>
-      <c r="G75" s="2" t="n"/>
-      <c r="H75" s="2" t="n"/>
-      <c r="I75" s="2" t="n"/>
+      <c r="A75" t="n">
+        <v>69</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>8809438484961</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Enough Rich Gold Intensive Pro Nourishing Cream</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="5" t="n"/>
+      <c r="I75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>8809541280269</t>
+          <t>8809726960405</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
+          <t>Enough Ultra X10 Collagen Pro Marine Cream</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F76" s="5" t="n"/>
       <c r="G76" s="5" t="n"/>
@@ -2409,25 +2449,25 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>8809210034087</t>
+          <t>8809726960399</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
+          <t>Enough Ultra X10 Collagen Pro Sun Cream</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F77" s="5" t="n"/>
       <c r="G77" s="5" t="n"/>
@@ -2436,21 +2476,21 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>8809541280238</t>
+          <t>8809280062362</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
+          <t>Enough collagen moisture foundation 13 тон</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
@@ -2463,21 +2503,21 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>8809541280245</t>
+          <t>8809280062379</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
+          <t>Enough collagen moisture foundation 21 тон</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
@@ -2490,25 +2530,25 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>8809541280283</t>
+          <t>8809280062386</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
+          <t>Enough collagen moisture foundation 23 тон</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F80" s="5" t="n"/>
       <c r="G80" s="5" t="n"/>
@@ -2517,25 +2557,25 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>8809541280160</t>
+          <t>8809474497062</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
+          <t>Enough collagen whitening moisture foundation 13 тон</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F81" s="5" t="n"/>
       <c r="G81" s="5" t="n"/>
@@ -2544,25 +2584,25 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>8809541280146</t>
+          <t>8809474497079</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
+          <t>Enough collagen whitening moisture foundation 21 тон</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F82" s="5" t="n"/>
       <c r="G82" s="5" t="n"/>
@@ -2571,25 +2611,25 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>8809541282447</t>
+          <t>8809605870856</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
+          <t>Enough collagen whitening moisture foundation 23 тон</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F83" s="5" t="n"/>
       <c r="G83" s="5" t="n"/>
@@ -2598,25 +2638,21 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>8809541280177</t>
-        </is>
-      </c>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
+          <t>Enough gold snail moisture foundation 23 тон</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F84" s="5" t="n"/>
       <c r="G84" s="5" t="n"/>
@@ -2625,25 +2661,25 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>8809541280214</t>
+          <t>8809605871952</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
+          <t>Enough rich gold double wear radiance foundation 23 тон</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F85" s="5" t="n"/>
       <c r="G85" s="5" t="n"/>
@@ -2651,53 +2687,41 @@
       <c r="I85" s="5" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v>76</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>8809541280207</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F86" s="5" t="n"/>
-      <c r="G86" s="5" t="n"/>
-      <c r="H86" s="5" t="n"/>
-      <c r="I86" s="5" t="n"/>
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>ETUDE</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="n"/>
+      <c r="I86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>8809541280184</t>
+          <t>8809668028041</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
+          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [160ml] / Пенка с содой для глубокого очищения и снятия макияжа</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F87" s="5" t="n"/>
       <c r="G87" s="5" t="n"/>
@@ -2706,25 +2730,25 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>8809541282508</t>
+          <t>8809668028058</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
+          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [30ml] / Пенка с содой для глубокого очищения</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F88" s="5" t="n"/>
       <c r="G88" s="5" t="n"/>
@@ -2733,21 +2757,21 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>8809541280221</t>
+          <t>8809820683118</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
@@ -2760,25 +2784,25 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>8809541280191</t>
+          <t>8809820692707</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F90" s="5" t="n"/>
       <c r="G90" s="5" t="n"/>
@@ -2787,25 +2811,25 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>8809541280153</t>
+          <t>8809668028089</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
+          <t>ETUDE - Baking Powder Pore Cleansing Foam [160ml] / Пенка для умывания с содой</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F91" s="5" t="n"/>
       <c r="G91" s="5" t="n"/>
@@ -2813,49 +2837,37 @@
       <c r="I91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" t="n">
-        <v>82</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>8809541280252</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F92" s="5" t="n"/>
-      <c r="G92" s="5" t="n"/>
-      <c r="H92" s="5" t="n"/>
-      <c r="I92" s="5" t="n"/>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="2" t="n"/>
+      <c r="H92" s="2" t="n"/>
+      <c r="I92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>8809541280276</t>
+          <t>8809595053659</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
@@ -2868,21 +2880,21 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>8809210034124</t>
+          <t>8809034583617</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
@@ -2895,21 +2907,21 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>8809210036517</t>
+          <t>8800260032009</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
@@ -2922,25 +2934,25 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>8809541282461</t>
+          <t>8809317289472</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F96" s="5" t="n"/>
       <c r="G96" s="5" t="n"/>
@@ -2949,21 +2961,21 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>8809541280139</t>
+          <t>8802221001338</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
@@ -2975,41 +2987,53 @@
       <c r="I97" s="5" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n"/>
-      <c r="E98" s="3" t="n"/>
-      <c r="F98" s="2" t="n"/>
-      <c r="G98" s="2" t="n"/>
-      <c r="H98" s="2" t="n"/>
-      <c r="I98" s="2" t="n"/>
+      <c r="A98" t="n">
+        <v>90</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>8809480772504</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="5" t="n"/>
+      <c r="I98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>8809794737022</t>
+          <t>8809595053284</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>JMSOLUTION  JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea] / Тканевая маска</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F99" s="5" t="n"/>
       <c r="G99" s="5" t="n"/>
@@ -3018,25 +3042,25 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>8809505547667</t>
+          <t>8809317289274</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F100" s="5" t="n"/>
       <c r="G100" s="5" t="n"/>
@@ -3045,25 +3069,25 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>8809505547698</t>
+          <t>8809480770975</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F101" s="5" t="n"/>
       <c r="G101" s="5" t="n"/>
@@ -3072,25 +3096,25 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>8809505547636</t>
+          <t>8809469772778</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F102" s="5" t="n"/>
       <c r="G102" s="5" t="n"/>
@@ -3098,49 +3122,41 @@
       <c r="I102" s="5" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" t="n">
-        <v>92</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] - ассорти набор из 10шт</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F103" s="5" t="n"/>
-      <c r="G103" s="5" t="n"/>
-      <c r="H103" s="5" t="n"/>
-      <c r="I103" s="5" t="n"/>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>HEIMISH</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="3" t="n"/>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="2" t="n"/>
+      <c r="H103" s="2" t="n"/>
+      <c r="I103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>HEIMISH</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>8809852542087</t>
+          <t>8809481760463</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea] / Тканевая маска для лица с экстрактом кордицепса и комплексом аминокислот</t>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F104" s="5" t="n"/>
       <c r="G104" s="5" t="n"/>
@@ -3148,53 +3164,41 @@
       <c r="I104" s="5" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" t="n">
-        <v>94</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>8809852540526</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea] / Ультраувлажняющая тканевая маска</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F105" s="5" t="n"/>
-      <c r="G105" s="5" t="n"/>
-      <c r="H105" s="5" t="n"/>
-      <c r="I105" s="5" t="n"/>
+      <c r="A105" s="2" t="n"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="3" t="n"/>
+      <c r="F105" s="2" t="n"/>
+      <c r="G105" s="2" t="n"/>
+      <c r="H105" s="2" t="n"/>
+      <c r="I105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>8809696353658</t>
+          <t>8809541280269</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
+          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F106" s="5" t="n"/>
       <c r="G106" s="5" t="n"/>
@@ -3203,25 +3207,25 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>8809711711531</t>
+          <t>8809210034087</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F107" s="5" t="n"/>
       <c r="G107" s="5" t="n"/>
@@ -3230,25 +3234,25 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>8809696354129</t>
+          <t>8809541280238</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
+          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F108" s="5" t="n"/>
       <c r="G108" s="5" t="n"/>
@@ -3257,25 +3261,25 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>8809711712491</t>
+          <t>8809541280245</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F109" s="5" t="n"/>
       <c r="G109" s="5" t="n"/>
@@ -3283,41 +3287,53 @@
       <c r="I109" s="5" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n"/>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>LEBELAGE</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n"/>
-      <c r="E110" s="3" t="n"/>
-      <c r="F110" s="2" t="n"/>
-      <c r="G110" s="2" t="n"/>
-      <c r="H110" s="2" t="n"/>
-      <c r="I110" s="2" t="n"/>
+      <c r="A110" t="n">
+        <v>100</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>8809541280283</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F110" s="5" t="n"/>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="5" t="n"/>
+      <c r="I110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LEBELAGE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>8809445616553</t>
+          <t>8809541280160</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
+          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F111" s="5" t="n"/>
       <c r="G111" s="5" t="n"/>
@@ -3325,37 +3341,49 @@
       <c r="I111" s="5" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n"/>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n"/>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="2" t="n"/>
-      <c r="G112" s="2" t="n"/>
-      <c r="H112" s="2" t="n"/>
-      <c r="I112" s="2" t="n"/>
+      <c r="A112" t="n">
+        <v>102</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>8809541280146</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F112" s="5" t="n"/>
+      <c r="G112" s="5" t="n"/>
+      <c r="H112" s="5" t="n"/>
+      <c r="I112" s="5" t="n"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>8809730950881</t>
+          <t>8809541282447</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>BIFIDA BIOME AMPOULE TONER 210ml</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
@@ -3368,21 +3396,21 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>8809730952236</t>
+          <t>8809541280177</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
+          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
@@ -3395,21 +3423,21 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>8809657114687</t>
+          <t>8809541280214</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
@@ -3422,21 +3450,21 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>8809730952014</t>
+          <t>8809541280207</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
@@ -3449,21 +3477,21 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>8809082392292</t>
+          <t>8809541280184</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
@@ -3476,25 +3504,25 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>8809567929722</t>
+          <t>8809541282508</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F118" s="5" t="n"/>
       <c r="G118" s="5" t="n"/>
@@ -3503,25 +3531,25 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>8809730957705</t>
+          <t>8809541280221</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
+          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F119" s="5" t="n"/>
       <c r="G119" s="5" t="n"/>
@@ -3529,41 +3557,53 @@
       <c r="I119" s="5" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n"/>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>MEDICUBE</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" s="3" t="n"/>
-      <c r="F120" s="2" t="n"/>
-      <c r="G120" s="2" t="n"/>
-      <c r="H120" s="2" t="n"/>
-      <c r="I120" s="2" t="n"/>
+      <c r="A120" t="n">
+        <v>110</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>8809541280191</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F120" s="5" t="n"/>
+      <c r="G120" s="5" t="n"/>
+      <c r="H120" s="5" t="n"/>
+      <c r="I120" s="5" t="n"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MEDICUBE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>8800256118885</t>
+          <t>8809541280153</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>PDRN PINK COLLAGEN CAPSULE CREAM 55g</t>
+          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F121" s="5" t="n"/>
       <c r="G121" s="5" t="n"/>
@@ -3572,25 +3612,25 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MEDICUBE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>8800256115532</t>
+          <t>8809541280252</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>PDRN PINK EXOSOME SHOT SERUM 2000 30ml</t>
+          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F122" s="5" t="n"/>
       <c r="G122" s="5" t="n"/>
@@ -3599,25 +3639,25 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MEDICUBE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>8800256115549</t>
+          <t>8809541280276</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>PDRN PINK EXOSOME SHOT SERUM 7500 30ml</t>
+          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F123" s="5" t="n"/>
       <c r="G123" s="5" t="n"/>
@@ -3626,25 +3666,25 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MEDICUBE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>8800256113101</t>
+          <t>8809210034124</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>PDRN PINK HYALURONIC MOISTURIZING CREAM 50ml</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F124" s="5" t="n"/>
       <c r="G124" s="5" t="n"/>
@@ -3653,25 +3693,25 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MEDICUBE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>8800256108053</t>
+          <t>8809210036517</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>PDRN PINK PEPTIDE SERUM 30ml</t>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F125" s="5" t="n"/>
       <c r="G125" s="5" t="n"/>
@@ -3680,25 +3720,25 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MEDICUBE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>8800256119660</t>
+          <t>8809541282461</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>TXA NIACINAMIDE CAPSULE CREAM 55g</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F126" s="5" t="n"/>
       <c r="G126" s="5" t="n"/>
@@ -3706,68 +3746,68 @@
       <c r="I126" s="5" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n"/>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n"/>
-      <c r="E127" s="3" t="n"/>
-      <c r="F127" s="2" t="n"/>
-      <c r="G127" s="2" t="n"/>
-      <c r="H127" s="2" t="n"/>
-      <c r="I127" s="2" t="n"/>
+      <c r="A127" t="n">
+        <v>117</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>8809541280139</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F127" s="5" t="n"/>
+      <c r="G127" s="5" t="n"/>
+      <c r="H127" s="5" t="n"/>
+      <c r="I127" s="5" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" t="n">
-        <v>113</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>8809508850429</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="F128" s="5" t="n"/>
-      <c r="G128" s="5" t="n"/>
-      <c r="H128" s="5" t="n"/>
-      <c r="I128" s="5" t="n"/>
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="3" t="n"/>
+      <c r="F128" s="2" t="n"/>
+      <c r="G128" s="2" t="n"/>
+      <c r="H128" s="2" t="n"/>
+      <c r="I128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>8809508850450</t>
+          <t>8809794737022</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
+          <t>JMSOLUTION  JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea] / Тканевая маска</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F129" s="5" t="n"/>
       <c r="G129" s="5" t="n"/>
@@ -3776,21 +3816,21 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>8809508850559</t>
+          <t>8809505547667</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
+          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
@@ -3803,25 +3843,25 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>8809508850566</t>
+          <t>8809505547698</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
+          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F131" s="5" t="n"/>
       <c r="G131" s="5" t="n"/>
@@ -3830,21 +3870,21 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>8809508851662</t>
+          <t>8809505547636</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
@@ -3857,25 +3897,21 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>8809508850504</t>
-        </is>
-      </c>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] - ассорти набор из 10шт</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F133" s="5" t="n"/>
       <c r="G133" s="5" t="n"/>
@@ -3884,17 +3920,21 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>8809852542087</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
+          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea] / Тканевая маска для лица с экстрактом кордицепса и комплексом аминокислот</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
@@ -3907,25 +3947,25 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>8809239801820</t>
+          <t>8809852540526</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
+          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea] / Ультраувлажняющая тканевая маска</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F135" s="5" t="n"/>
       <c r="G135" s="5" t="n"/>
@@ -3934,25 +3974,25 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>8809508850191</t>
+          <t>8809696353658</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
+          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F136" s="5" t="n"/>
       <c r="G136" s="5" t="n"/>
@@ -3961,21 +4001,21 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>8809508850696</t>
+          <t>8809711711531</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
+          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
@@ -3988,25 +4028,25 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>8809508850689</t>
+          <t>8809696354129</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
+          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F138" s="5" t="n"/>
       <c r="G138" s="5" t="n"/>
@@ -4015,21 +4055,21 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>8809508850412</t>
+          <t>8809711712491</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / Успокаивающие гидрогелевые патчи для глаз с экстрактом ромашки</t>
+          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
@@ -4041,53 +4081,41 @@
       <c r="I139" s="5" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" t="n">
-        <v>125</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>8809239800458</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="F140" s="5" t="n"/>
-      <c r="G140" s="5" t="n"/>
-      <c r="H140" s="5" t="n"/>
-      <c r="I140" s="5" t="n"/>
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>LANEIGE</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" s="3" t="n"/>
+      <c r="F140" s="2" t="n"/>
+      <c r="G140" s="2" t="n"/>
+      <c r="H140" s="2" t="n"/>
+      <c r="I140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>LANEIGE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>8809239800618</t>
+          <t>8809685797173</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]/ гидрогелевые патчи с золотом и EGF</t>
+          <t>Laneige Lip Sleeping Mask Berry 3 ml</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F141" s="5" t="n"/>
       <c r="G141" s="5" t="n"/>
@@ -4095,53 +4123,41 @@
       <c r="I141" s="5" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" t="n">
-        <v>127</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>8809239802872</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F142" s="5" t="n"/>
-      <c r="G142" s="5" t="n"/>
-      <c r="H142" s="5" t="n"/>
-      <c r="I142" s="5" t="n"/>
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>LEBELAGE</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" s="3" t="n"/>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="2" t="n"/>
+      <c r="H142" s="2" t="n"/>
+      <c r="I142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>LEBELAGE</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>8809239802896</t>
+          <t>8809445616553</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F143" s="5" t="n"/>
       <c r="G143" s="5" t="n"/>
@@ -4149,49 +4165,41 @@
       <c r="I143" s="5" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" t="n">
-        <v>129</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="F144" s="5" t="n"/>
-      <c r="G144" s="5" t="n"/>
-      <c r="H144" s="5" t="n"/>
-      <c r="I144" s="5" t="n"/>
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="3" t="n"/>
+      <c r="F144" s="2" t="n"/>
+      <c r="G144" s="2" t="n"/>
+      <c r="H144" s="2" t="n"/>
+      <c r="I144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>8809239803596</t>
+          <t>8809730950881</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
+          <t>BIFIDA BIOME AMPOULE TONER 210ml</t>
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F145" s="5" t="n"/>
       <c r="G145" s="5" t="n"/>
@@ -4200,21 +4208,21 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>8809239803589</t>
+          <t>8809730952236</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
@@ -4227,25 +4235,25 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>8809508850498</t>
+          <t>8809657114687</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F147" s="5" t="n"/>
       <c r="G147" s="5" t="n"/>
@@ -4253,37 +4261,49 @@
       <c r="I147" s="5" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n"/>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" s="3" t="n"/>
-      <c r="F148" s="2" t="n"/>
-      <c r="G148" s="2" t="n"/>
-      <c r="H148" s="2" t="n"/>
-      <c r="I148" s="2" t="n"/>
+      <c r="A148" t="n">
+        <v>134</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>8809730952014</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F148" s="5" t="n"/>
+      <c r="G148" s="5" t="n"/>
+      <c r="H148" s="5" t="n"/>
+      <c r="I148" s="5" t="n"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>8809738599044</t>
+          <t>8809082392292</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>1025 DOKDO BUBBLE FOAM_150ml</t>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
@@ -4296,25 +4316,25 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>8809849802408</t>
+          <t>8809567929722</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>PINE CALMING CICA BODY WASH_400ml</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F150" s="5" t="n"/>
       <c r="G150" s="5" t="n"/>
@@ -4323,25 +4343,25 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>8809864754126</t>
+          <t>8809730957705</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>PINE CALMING CICA CLEANSER_150ml</t>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F151" s="5" t="n"/>
       <c r="G151" s="5" t="n"/>
@@ -4349,53 +4369,41 @@
       <c r="I151" s="5" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" t="n">
-        <v>136</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>8809962542137</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>PINE CALMING CICA CREAM PLUS_60ml</t>
-        </is>
-      </c>
-      <c r="E152" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F152" s="5" t="n"/>
-      <c r="G152" s="5" t="n"/>
-      <c r="H152" s="5" t="n"/>
-      <c r="I152" s="5" t="n"/>
+      <c r="A152" s="2" t="n"/>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>MEDICUBE</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" s="3" t="n"/>
+      <c r="F152" s="2" t="n"/>
+      <c r="G152" s="2" t="n"/>
+      <c r="H152" s="2" t="n"/>
+      <c r="I152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MEDICUBE</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>8809750462708</t>
+          <t>8800256118885</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>PINE CALMING CICA PAD_50pcs</t>
+          <t>PDRN PINK COLLAGEN CAPSULE CREAM 55g</t>
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F153" s="5" t="n"/>
       <c r="G153" s="5" t="n"/>
@@ -4404,25 +4412,25 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MEDICUBE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>8809738608364</t>
+          <t>8800256115532</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+          <t>PDRN PINK EXOSOME SHOT SERUM 2000 30ml</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F154" s="5" t="n"/>
       <c r="G154" s="5" t="n"/>
@@ -4431,25 +4439,25 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MEDICUBE</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>8809657114731</t>
+          <t>8800256115549</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+          <t>PDRN PINK EXOSOME SHOT SERUM 7500 30ml</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F155" s="5" t="n"/>
       <c r="G155" s="5" t="n"/>
@@ -4458,25 +4466,25 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MEDICUBE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>8809738600221</t>
+          <t>8800256113101</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+          <t>PDRN PINK HYALURONIC MOISTURIZING CREAM 50ml</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F156" s="5" t="n"/>
       <c r="G156" s="5" t="n"/>
@@ -4485,25 +4493,25 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MEDICUBE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>8809962541840</t>
+          <t>8800256108053</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ROUND LAB CAMELLIA DEEP COLLAGEN FIRMING CREAM_50ml</t>
+          <t>PDRN PINK PEPTIDE SERUM 30ml</t>
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F157" s="5" t="n"/>
       <c r="G157" s="5" t="n"/>
@@ -4512,25 +4520,25 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MEDICUBE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>8809738593080</t>
+          <t>8800256119660</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+          <t>TXA NIACINAMIDE CAPSULE CREAM 55g</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F158" s="5" t="n"/>
       <c r="G158" s="5" t="n"/>
@@ -4538,31 +4546,19 @@
       <c r="I158" s="5" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" t="n">
-        <v>143</v>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>8809783325667</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
-        </is>
-      </c>
-      <c r="E159" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F159" s="5" t="n"/>
-      <c r="G159" s="5" t="n"/>
-      <c r="H159" s="5" t="n"/>
-      <c r="I159" s="5" t="n"/>
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>NOUGH</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" s="3" t="n"/>
+      <c r="F159" s="2" t="n"/>
+      <c r="G159" s="2" t="n"/>
+      <c r="H159" s="2" t="n"/>
+      <c r="I159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -4570,21 +4566,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>8809962540553</t>
-        </is>
-      </c>
+          <t>NOUGH</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ROUND LAB STICK POUCH KIT</t>
+          <t>NOUGH Collagen 3x Moisture Mist</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F160" s="5" t="n"/>
       <c r="G160" s="5" t="n"/>
@@ -4592,46 +4584,46 @@
       <c r="I160" s="5" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" t="n">
+      <c r="A161" s="2" t="n"/>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="3" t="n"/>
+      <c r="F161" s="2" t="n"/>
+      <c r="G161" s="2" t="n"/>
+      <c r="H161" s="2" t="n"/>
+      <c r="I161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
         <v>145</v>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>8809738593240</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>SOYBEAN SERUM_50ml</t>
-        </is>
-      </c>
-      <c r="E161" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F161" s="5" t="n"/>
-      <c r="G161" s="5" t="n"/>
-      <c r="H161" s="5" t="n"/>
-      <c r="I161" s="5" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="n"/>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>SKIN1004</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" s="3" t="n"/>
-      <c r="F162" s="2" t="n"/>
-      <c r="G162" s="2" t="n"/>
-      <c r="H162" s="2" t="n"/>
-      <c r="I162" s="2" t="n"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>8809508850429</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F162" s="5" t="n"/>
+      <c r="G162" s="5" t="n"/>
+      <c r="H162" s="5" t="n"/>
+      <c r="I162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -4639,17 +4631,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>8809576260601</t>
+          <t>8809508850450</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
@@ -4666,21 +4658,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>8809576261134</t>
+          <t>8809508850559</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>SKIN1004 Madagascar Centella Soothing Cream 75ml</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F164" s="5" t="n"/>
       <c r="G164" s="5" t="n"/>
@@ -4693,17 +4685,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>8809576261172</t>
+          <t>8809508850566</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>SKIN1004 Madagascar Centella Tone Brightening Capsule Ampoule 100ml</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
         </is>
       </c>
       <c r="E165" s="4" t="n">
@@ -4715,37 +4707,49 @@
       <c r="I165" s="5" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n"/>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>SOME BY MI</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n"/>
-      <c r="E166" s="3" t="n"/>
-      <c r="F166" s="2" t="n"/>
-      <c r="G166" s="2" t="n"/>
-      <c r="H166" s="2" t="n"/>
-      <c r="I166" s="2" t="n"/>
+      <c r="A166" t="n">
+        <v>149</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>8809508851662</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F166" s="5" t="n"/>
+      <c r="G166" s="5" t="n"/>
+      <c r="H166" s="5" t="n"/>
+      <c r="I166" s="5" t="n"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SOME BY MI</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>8809326334224</t>
+          <t>8809508850504</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
@@ -4757,37 +4761,49 @@
       <c r="I167" s="5" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n"/>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>THE ORDINARY</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n"/>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" s="3" t="n"/>
-      <c r="F168" s="2" t="n"/>
-      <c r="G168" s="2" t="n"/>
-      <c r="H168" s="2" t="n"/>
-      <c r="I168" s="2" t="n"/>
+      <c r="A168" t="n">
+        <v>151</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F168" s="5" t="n"/>
+      <c r="G168" s="5" t="n"/>
+      <c r="H168" s="5" t="n"/>
+      <c r="I168" s="5" t="n"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>THE ORDINARY</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>8809239801820</t>
+        </is>
+      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F169" s="5" t="n"/>
       <c r="G169" s="5" t="n"/>
@@ -4795,33 +4811,49 @@
       <c r="I169" s="5" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n"/>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n"/>
-      <c r="D170" s="2" t="n"/>
-      <c r="E170" s="3" t="n"/>
-      <c r="F170" s="2" t="n"/>
-      <c r="G170" s="2" t="n"/>
-      <c r="H170" s="2" t="n"/>
-      <c r="I170" s="2" t="n"/>
+      <c r="A170" t="n">
+        <v>153</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>8809508850191</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F170" s="5" t="n"/>
+      <c r="G170" s="5" t="n"/>
+      <c r="H170" s="5" t="n"/>
+      <c r="I170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>8809508850696</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
@@ -4834,21 +4866,21 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>VT COSMETICS</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>8803463006501</t>
+          <t>8809508850689</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VT REEDLE S LIP PLUMPER EXPERT</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
@@ -4861,21 +4893,25 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr"/>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>8809508850412</t>
+        </is>
+      </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / Успокаивающие гидрогелевые патчи для глаз с экстрактом ромашки</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F173" s="5" t="n"/>
       <c r="G173" s="5" t="n"/>
@@ -4883,25 +4919,905 @@
       <c r="I173" s="5" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="6" t="n"/>
-      <c r="B174" s="6" t="inlineStr">
+      <c r="A174" t="n">
+        <v>157</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>8809239800458</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F174" s="5" t="n"/>
+      <c r="G174" s="5" t="n"/>
+      <c r="H174" s="5" t="n"/>
+      <c r="I174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>158</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>8809239800618</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]/ гидрогелевые патчи с золотом и EGF</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F175" s="5" t="n"/>
+      <c r="G175" s="5" t="n"/>
+      <c r="H175" s="5" t="n"/>
+      <c r="I175" s="5" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>159</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>8809239802872</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F176" s="5" t="n"/>
+      <c r="G176" s="5" t="n"/>
+      <c r="H176" s="5" t="n"/>
+      <c r="I176" s="5" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>160</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>8809239802896</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F177" s="5" t="n"/>
+      <c r="G177" s="5" t="n"/>
+      <c r="H177" s="5" t="n"/>
+      <c r="I177" s="5" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>161</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F178" s="5" t="n"/>
+      <c r="G178" s="5" t="n"/>
+      <c r="H178" s="5" t="n"/>
+      <c r="I178" s="5" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>162</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>8809239803596</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F179" s="5" t="n"/>
+      <c r="G179" s="5" t="n"/>
+      <c r="H179" s="5" t="n"/>
+      <c r="I179" s="5" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>163</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>8809239803589</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F180" s="5" t="n"/>
+      <c r="G180" s="5" t="n"/>
+      <c r="H180" s="5" t="n"/>
+      <c r="I180" s="5" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>164</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>8809508850498</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F181" s="5" t="n"/>
+      <c r="G181" s="5" t="n"/>
+      <c r="H181" s="5" t="n"/>
+      <c r="I181" s="5" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>PRRETI</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" s="3" t="n"/>
+      <c r="F182" s="2" t="n"/>
+      <c r="G182" s="2" t="n"/>
+      <c r="H182" s="2" t="n"/>
+      <c r="I182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>165</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PRRETI</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>PRRETI Honey&amp;Berry Lip Sleeping Mask 15 гр</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F183" s="5" t="n"/>
+      <c r="G183" s="5" t="n"/>
+      <c r="H183" s="5" t="n"/>
+      <c r="I183" s="5" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n"/>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="n"/>
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" s="3" t="n"/>
+      <c r="F184" s="2" t="n"/>
+      <c r="G184" s="2" t="n"/>
+      <c r="H184" s="2" t="n"/>
+      <c r="I184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>166</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>8809738599044</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>1025 DOKDO BUBBLE FOAM_150ml</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F185" s="5" t="n"/>
+      <c r="G185" s="5" t="n"/>
+      <c r="H185" s="5" t="n"/>
+      <c r="I185" s="5" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>167</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>8809849802408</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>PINE CALMING CICA BODY WASH_400ml</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F186" s="5" t="n"/>
+      <c r="G186" s="5" t="n"/>
+      <c r="H186" s="5" t="n"/>
+      <c r="I186" s="5" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>168</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>8809864754126</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>PINE CALMING CICA CLEANSER_150ml</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F187" s="5" t="n"/>
+      <c r="G187" s="5" t="n"/>
+      <c r="H187" s="5" t="n"/>
+      <c r="I187" s="5" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>169</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>8809962542137</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>PINE CALMING CICA CREAM PLUS_60ml</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F188" s="5" t="n"/>
+      <c r="G188" s="5" t="n"/>
+      <c r="H188" s="5" t="n"/>
+      <c r="I188" s="5" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>170</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>8809750462708</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>PINE CALMING CICA PAD_50pcs</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F189" s="5" t="n"/>
+      <c r="G189" s="5" t="n"/>
+      <c r="H189" s="5" t="n"/>
+      <c r="I189" s="5" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>171</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>8809738608364</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F190" s="5" t="n"/>
+      <c r="G190" s="5" t="n"/>
+      <c r="H190" s="5" t="n"/>
+      <c r="I190" s="5" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>172</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>8809657114731</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+        </is>
+      </c>
+      <c r="E191" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F191" s="5" t="n"/>
+      <c r="G191" s="5" t="n"/>
+      <c r="H191" s="5" t="n"/>
+      <c r="I191" s="5" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>173</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>8809738600221</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F192" s="5" t="n"/>
+      <c r="G192" s="5" t="n"/>
+      <c r="H192" s="5" t="n"/>
+      <c r="I192" s="5" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>174</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>8809962541840</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ROUND LAB CAMELLIA DEEP COLLAGEN FIRMING CREAM_50ml</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F193" s="5" t="n"/>
+      <c r="G193" s="5" t="n"/>
+      <c r="H193" s="5" t="n"/>
+      <c r="I193" s="5" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>175</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>8809738593080</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F194" s="5" t="n"/>
+      <c r="G194" s="5" t="n"/>
+      <c r="H194" s="5" t="n"/>
+      <c r="I194" s="5" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>176</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>8809783325667</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F195" s="5" t="n"/>
+      <c r="G195" s="5" t="n"/>
+      <c r="H195" s="5" t="n"/>
+      <c r="I195" s="5" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>177</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>8809962540553</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ROUND LAB STICK POUCH KIT</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F196" s="5" t="n"/>
+      <c r="G196" s="5" t="n"/>
+      <c r="H196" s="5" t="n"/>
+      <c r="I196" s="5" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>178</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>8809738593240</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>SOYBEAN SERUM_50ml</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F197" s="5" t="n"/>
+      <c r="G197" s="5" t="n"/>
+      <c r="H197" s="5" t="n"/>
+      <c r="I197" s="5" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n"/>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="n"/>
+      <c r="D198" s="2" t="n"/>
+      <c r="E198" s="3" t="n"/>
+      <c r="F198" s="2" t="n"/>
+      <c r="G198" s="2" t="n"/>
+      <c r="H198" s="2" t="n"/>
+      <c r="I198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>179</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>8809576260601</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F199" s="5" t="n"/>
+      <c r="G199" s="5" t="n"/>
+      <c r="H199" s="5" t="n"/>
+      <c r="I199" s="5" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>180</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>8809576261134</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SKIN1004 Madagascar Centella Soothing Cream 75ml</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F200" s="5" t="n"/>
+      <c r="G200" s="5" t="n"/>
+      <c r="H200" s="5" t="n"/>
+      <c r="I200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>181</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>8809576261172</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>SKIN1004 Madagascar Centella Tone Brightening Capsule Ampoule 100ml</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F201" s="5" t="n"/>
+      <c r="G201" s="5" t="n"/>
+      <c r="H201" s="5" t="n"/>
+      <c r="I201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n"/>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="n"/>
+      <c r="D202" s="2" t="n"/>
+      <c r="E202" s="3" t="n"/>
+      <c r="F202" s="2" t="n"/>
+      <c r="G202" s="2" t="n"/>
+      <c r="H202" s="2" t="n"/>
+      <c r="I202" s="2" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>182</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>8809326334224</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+        </is>
+      </c>
+      <c r="E203" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F203" s="5" t="n"/>
+      <c r="G203" s="5" t="n"/>
+      <c r="H203" s="5" t="n"/>
+      <c r="I203" s="5" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n"/>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>THE ORDINARY</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="n"/>
+      <c r="D204" s="2" t="n"/>
+      <c r="E204" s="3" t="n"/>
+      <c r="F204" s="2" t="n"/>
+      <c r="G204" s="2" t="n"/>
+      <c r="H204" s="2" t="n"/>
+      <c r="I204" s="2" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>183</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>THE ORDINARY</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F205" s="5" t="n"/>
+      <c r="G205" s="5" t="n"/>
+      <c r="H205" s="5" t="n"/>
+      <c r="I205" s="5" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n"/>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="n"/>
+      <c r="D206" s="2" t="n"/>
+      <c r="E206" s="3" t="n"/>
+      <c r="F206" s="2" t="n"/>
+      <c r="G206" s="2" t="n"/>
+      <c r="H206" s="2" t="n"/>
+      <c r="I206" s="2" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>184</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F207" s="5" t="n"/>
+      <c r="G207" s="5" t="n"/>
+      <c r="H207" s="5" t="n"/>
+      <c r="I207" s="5" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>185</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>8803463006501</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>VT REEDLE S LIP PLUMPER EXPERT</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F208" s="5" t="n"/>
+      <c r="G208" s="5" t="n"/>
+      <c r="H208" s="5" t="n"/>
+      <c r="I208" s="5" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>186</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F209" s="5" t="n"/>
+      <c r="G209" s="5" t="n"/>
+      <c r="H209" s="5" t="n"/>
+      <c r="I209" s="5" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="n"/>
+      <c r="B210" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C174" s="6" t="n"/>
-      <c r="D174" s="6" t="inlineStr">
-        <is>
-          <t>позиций: 153</t>
-        </is>
-      </c>
-      <c r="E174" s="7" t="n">
-        <v>58500</v>
-      </c>
-      <c r="F174" s="6" t="n"/>
-      <c r="G174" s="6" t="n"/>
-      <c r="H174" s="6" t="n"/>
-      <c r="I174" s="6" t="n"/>
+      <c r="C210" s="6" t="n"/>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t>позиций: 186</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="n">
+        <v>66900</v>
+      </c>
+      <c r="F210" s="6" t="n"/>
+      <c r="G210" s="6" t="n"/>
+      <c r="H210" s="6" t="n"/>
+      <c r="I210" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4914,7 +5830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4998,10 +5914,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3600</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="7">
@@ -5072,85 +5988,85 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LEBELAGE</t>
+          <t>LANEIGE</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>LEBELAGE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3200</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MEDICUBE</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MEDICUBE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>7000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>NOUGH</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4600</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1500</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SOME BY MI</t>
+          <t>PRRETI</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5163,40 +6079,79 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>THE ORDINARY</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>200</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VT COSMETICS</t>
+          <t>SKIN1004</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>3</v>
       </c>
       <c r="C20" s="4" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>THE ORDINARY</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="4" t="n">
         <v>1100</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>ВСЕГО</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n">
-        <v>153</v>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>58500</v>
+      <c r="B24" s="6" t="n">
+        <v>186</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>66900</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Заявка на весь ассортимент.xlsx
+++ b/outputs/Заявка на весь ассортимент.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I210"/>
+  <dimension ref="A1:I209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8809605872263</t>
+          <t>8809438489577</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
+          <t>ENOUGH Collagen 3x Moisture Mist</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>8809605872270</t>
+          <t>8809605872263</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
+          <t xml:space="preserve">ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка) </t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
@@ -1895,16 +1895,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8809605872287</t>
+          <t>8809605872270</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F56" s="5" t="n"/>
       <c r="G56" s="5" t="n"/>
@@ -1922,16 +1922,16 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8809474498809</t>
+          <t>8809605872287</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ENOUGH Gold snail moisture foundation #13</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F57" s="5" t="n"/>
       <c r="G57" s="5" t="n"/>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8809474498816</t>
+          <t>8809474498809</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ENOUGH Gold snail moisture foundation #21</t>
+          <t>ENOUGH Gold snail moisture foundation #13</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
@@ -1976,16 +1976,16 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>8809605871938</t>
+          <t>8809474498816</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ENOUGH Premium Rich Gold Double Wear Radiance Foundation #13</t>
+          <t>ENOUGH Gold snail moisture foundation #21</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F59" s="5" t="n"/>
       <c r="G59" s="5" t="n"/>
@@ -2003,16 +2003,16 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8809605871945</t>
+          <t>8809605871938</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ENOUGH Premium Rich Gold Double Wear Radiance Foundation #21</t>
+          <t>ENOUGH Premium Rich Gold Double Wear Radiance Foundation #13</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F60" s="5" t="n"/>
       <c r="G60" s="5" t="n"/>
@@ -2030,16 +2030,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>8809605870993</t>
+          <t>8809605871945</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ENOUGH Premium Ultra X10 cover up Collagen foundation #13</t>
+          <t>ENOUGH Premium Rich Gold Double Wear Radiance Foundation #21</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F61" s="5" t="n"/>
       <c r="G61" s="5" t="n"/>
@@ -2057,16 +2057,16 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>8809605871006</t>
+          <t>8809605870993</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ENOUGH Ultra X10 Cover Up Collagen Foundation 21 тон</t>
+          <t>ENOUGH Premium Ultra X10 cover up Collagen foundation #13</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F62" s="5" t="n"/>
       <c r="G62" s="5" t="n"/>
@@ -2084,16 +2084,16 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>8809605871013</t>
+          <t>8809605871006</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ENOUGH Ultra X10 Cover Up Collagen Foundation 23 тон</t>
+          <t>ENOUGH Ultra X10 Cover Up Collagen Foundation 21 тон</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F63" s="5" t="n"/>
       <c r="G63" s="5" t="n"/>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>8809438484954</t>
+          <t>8809605871013</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Enough 8 Peptide Sensation Pro Balancing Cream</t>
+          <t>ENOUGH Ultra X10 Cover Up Collagen Foundation 23 тон</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>8809726960375</t>
+          <t>8809438484954</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Enough 8 Peptide Sensation Pro Sun Cream</t>
+          <t>Enough 8 Peptide Sensation Pro Balancing Cream</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
@@ -2165,16 +2165,16 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>8809605870962</t>
+          <t>8809726960375</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Enough 8 Peptide full cover perfect foundation 13 тон</t>
+          <t>Enough 8 Peptide Sensation Pro Sun Cream</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F66" s="5" t="n"/>
       <c r="G66" s="5" t="n"/>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>8809605870979</t>
+          <t>8809605870962</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Enough 8 Peptide full cover perfect foundation 21 тон</t>
+          <t>Enough 8 Peptide full cover perfect foundation 13 тон</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
@@ -2219,16 +2219,16 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>8809605870986</t>
+          <t>8809605870979</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Enough 8 Peptide full cover perfect foundation 23 тон</t>
+          <t>Enough 8 Peptide full cover perfect foundation 21 тон</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F68" s="5" t="n"/>
       <c r="G68" s="5" t="n"/>
@@ -2244,10 +2244,14 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>8809605870986</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Enough Collagen 3X Moisture Cream</t>
+          <t>Enough 8 Peptide full cover perfect foundation 23 тон</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
@@ -2267,14 +2271,10 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>8809438489584</t>
-        </is>
-      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Enough Collagen 3X Moisture Makeup Fixer</t>
+          <t>Enough Collagen 3X Moisture Cream</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>8809951050636</t>
+          <t>8809438489584</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Enough Collagen 3X Moisture Stick Foundation SPF50 PA++++ 13N</t>
+          <t>Enough Collagen 3X Moisture Makeup Fixer</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>8809951050643</t>
+          <t>8809951050636</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Enough Collagen 3X Moisture Stick Foundation SPF50 PA++++ 21N</t>
+          <t>Enough Collagen 3X Moisture Stick Foundation SPF50 PA++++ 13N</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>8809755465285</t>
+          <t>8809951050643</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Enough Collagen 3X Moisture Sun Cream</t>
+          <t>Enough Collagen 3X Moisture Stick Foundation SPF50 PA++++ 21N</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>8809541378546</t>
+          <t>8809755465285</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Enough Collagen 3x Moisture Ampoule</t>
+          <t>Enough Collagen 3X Moisture Sun Cream</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>8809438484961</t>
+          <t>8809541378546</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Enough Rich Gold Intensive Pro Nourishing Cream</t>
+          <t>Enough Collagen 3x Moisture Ampoule</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
@@ -2431,12 +2431,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>8809726960405</t>
+          <t>8809438484961</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Enough Ultra X10 Collagen Pro Marine Cream</t>
+          <t>Enough Rich Gold Intensive Pro Nourishing Cream</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>8809726960399</t>
+          <t>8809726960405</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Enough Ultra X10 Collagen Pro Sun Cream</t>
+          <t>Enough Ultra X10 Collagen Pro Marine Cream</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
@@ -2485,16 +2485,16 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>8809280062362</t>
+          <t>8809726960399</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Enough collagen moisture foundation 13 тон</t>
+          <t>Enough Ultra X10 Collagen Pro Sun Cream</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F78" s="5" t="n"/>
       <c r="G78" s="5" t="n"/>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>8809280062379</t>
+          <t>8809280062362</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Enough collagen moisture foundation 21 тон</t>
+          <t>Enough collagen moisture foundation 13 тон</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
@@ -2539,16 +2539,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>8809280062386</t>
+          <t>8809280062379</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Enough collagen moisture foundation 23 тон</t>
+          <t>Enough collagen moisture foundation 21 тон</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F80" s="5" t="n"/>
       <c r="G80" s="5" t="n"/>
@@ -2566,16 +2566,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>8809474497062</t>
+          <t>8809280062386</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Enough collagen whitening moisture foundation 13 тон</t>
+          <t>Enough collagen moisture foundation 23 тон</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F81" s="5" t="n"/>
       <c r="G81" s="5" t="n"/>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>8809474497079</t>
+          <t>8809474497062</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Enough collagen whitening moisture foundation 21 тон</t>
+          <t>Enough collagen whitening moisture foundation 13 тон</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>8809605870856</t>
+          <t>8809474497079</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Enough collagen whitening moisture foundation 23 тон</t>
+          <t>Enough collagen whitening moisture foundation 21 тон</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
@@ -2645,10 +2645,14 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>8809605870856</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Enough gold snail moisture foundation 23 тон</t>
+          <t>Enough collagen whitening moisture foundation 23 тон</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
@@ -2668,14 +2672,10 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>8809605871952</t>
-        </is>
-      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Enough rich gold double wear radiance foundation 23 тон</t>
+          <t>Enough gold snail moisture foundation 23 тон</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
@@ -2687,46 +2687,46 @@
       <c r="I85" s="5" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="A86" t="n">
+        <v>80</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>8809605871952</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Enough rich gold double wear radiance foundation 23 тон</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="5" t="n"/>
+      <c r="I86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>ETUDE</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="3" t="n"/>
-      <c r="F86" s="2" t="n"/>
-      <c r="G86" s="2" t="n"/>
-      <c r="H86" s="2" t="n"/>
-      <c r="I86" s="2" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>80</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>ETUDE</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>8809668028041</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [160ml] / Пенка с содой для глубокого очищения и снятия макияжа</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F87" s="5" t="n"/>
-      <c r="G87" s="5" t="n"/>
-      <c r="H87" s="5" t="n"/>
-      <c r="I87" s="5" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="n"/>
+      <c r="H87" s="2" t="n"/>
+      <c r="I87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>8809668028058</t>
+          <t>8809668028041</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [30ml] / Пенка с содой для глубокого очищения</t>
+          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [160ml] / Пенка с содой для глубокого очищения и снятия макияжа</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>8809820683118</t>
+          <t>8809668028058</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
+          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [30ml] / Пенка с содой для глубокого очищения</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F89" s="5" t="n"/>
       <c r="G89" s="5" t="n"/>
@@ -2793,16 +2793,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>8809820692707</t>
+          <t>8809820683118</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищающий скраб для лица с содой</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F90" s="5" t="n"/>
       <c r="G90" s="5" t="n"/>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>8809668028089</t>
+          <t>8809820692707</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Pore Cleansing Foam [160ml] / Пенка для умывания с содой</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищающий скраб для лица с содой</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
@@ -2837,46 +2837,46 @@
       <c r="I91" s="5" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="A92" t="n">
+        <v>85</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ETUDE</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>8809668028089</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder Pore Cleansing Foam [160ml] / Пенка для умывания с содой</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>FARMSTAY</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="3" t="n"/>
-      <c r="F92" s="2" t="n"/>
-      <c r="G92" s="2" t="n"/>
-      <c r="H92" s="2" t="n"/>
-      <c r="I92" s="2" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>85</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>8809595053659</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="n"/>
-      <c r="H93" s="5" t="n"/>
-      <c r="I93" s="5" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n"/>
+      <c r="E93" s="3" t="n"/>
+      <c r="F93" s="2" t="n"/>
+      <c r="G93" s="2" t="n"/>
+      <c r="H93" s="2" t="n"/>
+      <c r="I93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>8809034583617</t>
+          <t>8809595053659</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>8800260032009</t>
+          <t>8809034583617</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
@@ -2943,16 +2943,16 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>8809317289472</t>
+          <t>8800260032009</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F96" s="5" t="n"/>
       <c r="G96" s="5" t="n"/>
@@ -2970,16 +2970,16 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>8802221001338</t>
+          <t>8809317289472</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F97" s="5" t="n"/>
       <c r="G97" s="5" t="n"/>
@@ -2997,12 +2997,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>8809480772504</t>
+          <t>8802221001338</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>8809595053284</t>
+          <t>8809480772504</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>8809317289274</t>
+          <t>8809595053284</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>8809480770975</t>
+          <t>8809317289274</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>8809469772778</t>
+          <t>8809480770975</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
@@ -3122,88 +3122,88 @@
       <c r="I102" s="5" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="A103" t="n">
+        <v>95</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>8809469772778</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F103" s="5" t="n"/>
+      <c r="G103" s="5" t="n"/>
+      <c r="H103" s="5" t="n"/>
+      <c r="I103" s="5" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>HEIMISH</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="3" t="n"/>
-      <c r="F103" s="2" t="n"/>
-      <c r="G103" s="2" t="n"/>
-      <c r="H103" s="2" t="n"/>
-      <c r="I103" s="2" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>95</v>
-      </c>
-      <c r="B104" t="inlineStr">
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="3" t="n"/>
+      <c r="F104" s="2" t="n"/>
+      <c r="G104" s="2" t="n"/>
+      <c r="H104" s="2" t="n"/>
+      <c r="I104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>96</v>
+      </c>
+      <c r="B105" t="inlineStr">
         <is>
           <t>HEIMISH</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>8809481760463</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
         </is>
       </c>
-      <c r="E104" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F104" s="5" t="n"/>
-      <c r="G104" s="5" t="n"/>
-      <c r="H104" s="5" t="n"/>
-      <c r="I104" s="5" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n"/>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="E105" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F105" s="5" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="5" t="n"/>
+      <c r="I105" s="5" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>JIGOTT</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n"/>
-      <c r="E105" s="3" t="n"/>
-      <c r="F105" s="2" t="n"/>
-      <c r="G105" s="2" t="n"/>
-      <c r="H105" s="2" t="n"/>
-      <c r="I105" s="2" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>96</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>8809541280269</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F106" s="5" t="n"/>
-      <c r="G106" s="5" t="n"/>
-      <c r="H106" s="5" t="n"/>
-      <c r="I106" s="5" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="3" t="n"/>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="n"/>
+      <c r="H106" s="2" t="n"/>
+      <c r="I106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>8809210034087</t>
+          <t>8809541280269</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
+          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>8809541280238</t>
+          <t>8809210034087</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>8809541280245</t>
+          <t>8809541280238</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
+          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>8809541280283</t>
+          <t>8809541280245</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
+          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>8809541280160</t>
+          <t>8809541280283</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
+          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>8809541280146</t>
+          <t>8809541280160</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
+          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>8809541282447</t>
+          <t>8809541280146</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
+          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>8809541280177</t>
+          <t>8809541282447</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>8809541280214</t>
+          <t>8809541280177</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
+          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>8809541280207</t>
+          <t>8809541280214</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
+          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>8809541280184</t>
+          <t>8809541280207</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
+          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
@@ -3513,16 +3513,16 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>8809541282508</t>
+          <t>8809541280184</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
+          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F118" s="5" t="n"/>
       <c r="G118" s="5" t="n"/>
@@ -3540,16 +3540,16 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>8809541280221</t>
+          <t>8809541282508</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F119" s="5" t="n"/>
       <c r="G119" s="5" t="n"/>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>8809541280191</t>
+          <t>8809541280221</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
+          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>8809541280153</t>
+          <t>8809541280191</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
+          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>8809541280252</t>
+          <t>8809541280153</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
+          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>8809541280276</t>
+          <t>8809541280252</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
+          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>8809210034124</t>
+          <t>8809541280276</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
+          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>8809210036517</t>
+          <t>8809210034124</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
@@ -3729,16 +3729,16 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>8809541282461</t>
+          <t>8809210036517</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F126" s="5" t="n"/>
       <c r="G126" s="5" t="n"/>
@@ -3756,16 +3756,16 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>8809541280139</t>
+          <t>8809541282461</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F127" s="5" t="n"/>
       <c r="G127" s="5" t="n"/>
@@ -3773,46 +3773,46 @@
       <c r="I127" s="5" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n"/>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="A128" t="n">
+        <v>118</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>8809541280139</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F128" s="5" t="n"/>
+      <c r="G128" s="5" t="n"/>
+      <c r="H128" s="5" t="n"/>
+      <c r="I128" s="5" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n"/>
-      <c r="E128" s="3" t="n"/>
-      <c r="F128" s="2" t="n"/>
-      <c r="G128" s="2" t="n"/>
-      <c r="H128" s="2" t="n"/>
-      <c r="I128" s="2" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>118</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>8809794737022</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>JMSOLUTION  JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea] / Тканевая маска</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F129" s="5" t="n"/>
-      <c r="G129" s="5" t="n"/>
-      <c r="H129" s="5" t="n"/>
-      <c r="I129" s="5" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="3" t="n"/>
+      <c r="F129" s="2" t="n"/>
+      <c r="G129" s="2" t="n"/>
+      <c r="H129" s="2" t="n"/>
+      <c r="I129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>8809505547667</t>
+          <t>8809794737022</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
+          <t>JMSOLUTION  JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea] / Тканевая маска</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>8809505547698</t>
+          <t>8809505547667</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
+          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>8809505547636</t>
+          <t>8809505547698</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
+          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
@@ -3904,14 +3904,18 @@
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>8809505547636</t>
+        </is>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] - ассорти набор из 10шт</t>
+          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F133" s="5" t="n"/>
       <c r="G133" s="5" t="n"/>
@@ -3927,18 +3931,14 @@
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>8809852542087</t>
-        </is>
-      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea] / Тканевая маска для лица с экстрактом кордицепса и комплексом аминокислот</t>
+          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] - ассорти набор из 10шт</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F134" s="5" t="n"/>
       <c r="G134" s="5" t="n"/>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>8809852540526</t>
+          <t>8809852542087</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea] / Ультраувлажняющая тканевая маска</t>
+          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea] / Тканевая маска для лица с экстрактом кордицепса и комплексом аминокислот</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>8809696353658</t>
+          <t>8809852540526</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
+          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea] / Ультраувлажняющая тканевая маска</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>8809711711531</t>
+          <t>8809696353658</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
+          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>8809696354129</t>
+          <t>8809711711531</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
+          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>8809711712491</t>
+          <t>8809696354129</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
@@ -4081,130 +4081,130 @@
       <c r="I139" s="5" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n"/>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="A140" t="n">
+        <v>129</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>8809711712491</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F140" s="5" t="n"/>
+      <c r="G140" s="5" t="n"/>
+      <c r="H140" s="5" t="n"/>
+      <c r="I140" s="5" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>LANEIGE</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n"/>
-      <c r="E140" s="3" t="n"/>
-      <c r="F140" s="2" t="n"/>
-      <c r="G140" s="2" t="n"/>
-      <c r="H140" s="2" t="n"/>
-      <c r="I140" s="2" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>129</v>
-      </c>
-      <c r="B141" t="inlineStr">
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="3" t="n"/>
+      <c r="F141" s="2" t="n"/>
+      <c r="G141" s="2" t="n"/>
+      <c r="H141" s="2" t="n"/>
+      <c r="I141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>130</v>
+      </c>
+      <c r="B142" t="inlineStr">
         <is>
           <t>LANEIGE</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>8809685797173</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>Laneige Lip Sleeping Mask Berry 3 ml</t>
         </is>
       </c>
-      <c r="E141" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F141" s="5" t="n"/>
-      <c r="G141" s="5" t="n"/>
-      <c r="H141" s="5" t="n"/>
-      <c r="I141" s="5" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n"/>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="E142" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F142" s="5" t="n"/>
+      <c r="G142" s="5" t="n"/>
+      <c r="H142" s="5" t="n"/>
+      <c r="I142" s="5" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>LEBELAGE</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n"/>
-      <c r="E142" s="3" t="n"/>
-      <c r="F142" s="2" t="n"/>
-      <c r="G142" s="2" t="n"/>
-      <c r="H142" s="2" t="n"/>
-      <c r="I142" s="2" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>130</v>
-      </c>
-      <c r="B143" t="inlineStr">
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" s="3" t="n"/>
+      <c r="F143" s="2" t="n"/>
+      <c r="G143" s="2" t="n"/>
+      <c r="H143" s="2" t="n"/>
+      <c r="I143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>131</v>
+      </c>
+      <c r="B144" t="inlineStr">
         <is>
           <t>LEBELAGE</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>8809445616553</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
         </is>
       </c>
-      <c r="E143" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F143" s="5" t="n"/>
-      <c r="G143" s="5" t="n"/>
-      <c r="H143" s="5" t="n"/>
-      <c r="I143" s="5" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="n"/>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="E144" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F144" s="5" t="n"/>
+      <c r="G144" s="5" t="n"/>
+      <c r="H144" s="5" t="n"/>
+      <c r="I144" s="5" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>MANYO</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n"/>
-      <c r="E144" s="3" t="n"/>
-      <c r="F144" s="2" t="n"/>
-      <c r="G144" s="2" t="n"/>
-      <c r="H144" s="2" t="n"/>
-      <c r="I144" s="2" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>131</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>8809730950881</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>BIFIDA BIOME AMPOULE TONER 210ml</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F145" s="5" t="n"/>
-      <c r="G145" s="5" t="n"/>
-      <c r="H145" s="5" t="n"/>
-      <c r="I145" s="5" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="3" t="n"/>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="2" t="n"/>
+      <c r="H145" s="2" t="n"/>
+      <c r="I145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>8809730952236</t>
+          <t>8809730950881</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
+          <t>BIFIDA BIOME AMPOULE TONER 210ml</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>8809657114687</t>
+          <t>8809730952236</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>8809730952014</t>
+          <t>8809657114687</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>8809082392292</t>
+          <t>8809730952014</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>8809567929722</t>
+          <t>8809082392292</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
@@ -4352,16 +4352,16 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>8809730957705</t>
+          <t>8809567929722</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F151" s="5" t="n"/>
       <c r="G151" s="5" t="n"/>
@@ -4369,46 +4369,46 @@
       <c r="I151" s="5" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n"/>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="A152" t="n">
+        <v>138</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>8809730957705</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F152" s="5" t="n"/>
+      <c r="G152" s="5" t="n"/>
+      <c r="H152" s="5" t="n"/>
+      <c r="I152" s="5" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n"/>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>MEDICUBE</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" s="3" t="n"/>
-      <c r="F152" s="2" t="n"/>
-      <c r="G152" s="2" t="n"/>
-      <c r="H152" s="2" t="n"/>
-      <c r="I152" s="2" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>138</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>MEDICUBE</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>8800256118885</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>PDRN PINK COLLAGEN CAPSULE CREAM 55g</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F153" s="5" t="n"/>
-      <c r="G153" s="5" t="n"/>
-      <c r="H153" s="5" t="n"/>
-      <c r="I153" s="5" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" s="3" t="n"/>
+      <c r="F153" s="2" t="n"/>
+      <c r="G153" s="2" t="n"/>
+      <c r="H153" s="2" t="n"/>
+      <c r="I153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -4421,16 +4421,16 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>8800256115532</t>
+          <t>8800256118885</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>PDRN PINK EXOSOME SHOT SERUM 2000 30ml</t>
+          <t>PDRN PINK COLLAGEN CAPSULE CREAM 55g</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F154" s="5" t="n"/>
       <c r="G154" s="5" t="n"/>
@@ -4448,16 +4448,16 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>8800256115549</t>
+          <t>8800256115532</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>PDRN PINK EXOSOME SHOT SERUM 7500 30ml</t>
+          <t>PDRN PINK EXOSOME SHOT SERUM 2000 30ml</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F155" s="5" t="n"/>
       <c r="G155" s="5" t="n"/>
@@ -4475,16 +4475,16 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>8800256113101</t>
+          <t>8800256115549</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>PDRN PINK HYALURONIC MOISTURIZING CREAM 50ml</t>
+          <t>PDRN PINK EXOSOME SHOT SERUM 7500 30ml</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F156" s="5" t="n"/>
       <c r="G156" s="5" t="n"/>
@@ -4502,16 +4502,16 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>8800256108053</t>
+          <t>8800256113101</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>PDRN PINK PEPTIDE SERUM 30ml</t>
+          <t>PDRN PINK HYALURONIC MOISTURIZING CREAM 50ml</t>
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F157" s="5" t="n"/>
       <c r="G157" s="5" t="n"/>
@@ -4529,16 +4529,16 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>8800256119660</t>
+          <t>8800256108053</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>TXA NIACINAMIDE CAPSULE CREAM 55g</t>
+          <t>PDRN PINK PEPTIDE SERUM 30ml</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F158" s="5" t="n"/>
       <c r="G158" s="5" t="n"/>
@@ -4546,61 +4546,77 @@
       <c r="I158" s="5" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n"/>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>NOUGH</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n"/>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" s="3" t="n"/>
-      <c r="F159" s="2" t="n"/>
-      <c r="G159" s="2" t="n"/>
-      <c r="H159" s="2" t="n"/>
-      <c r="I159" s="2" t="n"/>
+      <c r="A159" t="n">
+        <v>144</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>MEDICUBE</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>8800256119660</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>TXA NIACINAMIDE CAPSULE CREAM 55g</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F159" s="5" t="n"/>
+      <c r="G159" s="5" t="n"/>
+      <c r="H159" s="5" t="n"/>
+      <c r="I159" s="5" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" t="n">
-        <v>144</v>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>NOUGH</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>NOUGH Collagen 3x Moisture Mist</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F160" s="5" t="n"/>
-      <c r="G160" s="5" t="n"/>
-      <c r="H160" s="5" t="n"/>
-      <c r="I160" s="5" t="n"/>
+      <c r="A160" s="2" t="n"/>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" s="3" t="n"/>
+      <c r="F160" s="2" t="n"/>
+      <c r="G160" s="2" t="n"/>
+      <c r="H160" s="2" t="n"/>
+      <c r="I160" s="2" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n"/>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="A161" t="n">
+        <v>145</v>
+      </c>
+      <c r="B161" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" s="3" t="n"/>
-      <c r="F161" s="2" t="n"/>
-      <c r="G161" s="2" t="n"/>
-      <c r="H161" s="2" t="n"/>
-      <c r="I161" s="2" t="n"/>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>8809508850429</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="F161" s="5" t="n"/>
+      <c r="G161" s="5" t="n"/>
+      <c r="H161" s="5" t="n"/>
+      <c r="I161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -4609,16 +4625,16 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>8809508850429</t>
+          <t>8809508850450</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F162" s="5" t="n"/>
       <c r="G162" s="5" t="n"/>
@@ -4627,7 +4643,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -4636,16 +4652,16 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>8809508850450</t>
+          <t>8809508850559</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F163" s="5" t="n"/>
       <c r="G163" s="5" t="n"/>
@@ -4654,7 +4670,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -4663,16 +4679,16 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>8809508850559</t>
+          <t>8809508850566</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F164" s="5" t="n"/>
       <c r="G164" s="5" t="n"/>
@@ -4681,7 +4697,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -4690,16 +4706,16 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>8809508850566</t>
+          <t>8809508851662</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F165" s="5" t="n"/>
       <c r="G165" s="5" t="n"/>
@@ -4708,7 +4724,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -4717,12 +4733,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>8809508851662</t>
+          <t>8809508850504</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
@@ -4735,21 +4751,17 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>8809508850504</t>
-        </is>
-      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
@@ -4762,21 +4774,25 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>8809239801820</t>
+        </is>
+      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F168" s="5" t="n"/>
       <c r="G168" s="5" t="n"/>
@@ -4785,7 +4801,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -4794,12 +4810,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>8809239801820</t>
+          <t>8809508850191</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
         </is>
       </c>
       <c r="E169" s="4" t="n">
@@ -4812,7 +4828,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -4821,16 +4837,16 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>8809508850191</t>
+          <t>8809508850696</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F170" s="5" t="n"/>
       <c r="G170" s="5" t="n"/>
@@ -4839,7 +4855,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -4848,16 +4864,16 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>8809508850696</t>
+          <t>8809508850689</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F171" s="5" t="n"/>
       <c r="G171" s="5" t="n"/>
@@ -4866,7 +4882,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -4875,16 +4891,16 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>8809508850689</t>
+          <t>8809508850412</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / Успокаивающие гидрогелевые патчи для глаз с экстрактом ромашки</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F172" s="5" t="n"/>
       <c r="G172" s="5" t="n"/>
@@ -4893,7 +4909,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -4902,16 +4918,16 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>8809508850412</t>
+          <t>8809239800458</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / Успокаивающие гидрогелевые патчи для глаз с экстрактом ромашки</t>
+          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F173" s="5" t="n"/>
       <c r="G173" s="5" t="n"/>
@@ -4920,7 +4936,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -4929,16 +4945,16 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>8809239800458</t>
+          <t>8809239800618</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
+          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]/ гидрогелевые патчи с золотом и EGF</t>
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F174" s="5" t="n"/>
       <c r="G174" s="5" t="n"/>
@@ -4947,7 +4963,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -4956,16 +4972,16 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>8809239800618</t>
+          <t>8809239802872</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]/ гидрогелевые патчи с золотом и EGF</t>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F175" s="5" t="n"/>
       <c r="G175" s="5" t="n"/>
@@ -4974,7 +4990,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -4983,16 +4999,16 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>8809239802872</t>
+          <t>8809239802896</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F176" s="5" t="n"/>
       <c r="G176" s="5" t="n"/>
@@ -5001,21 +5017,17 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>8809239802896</t>
-        </is>
-      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
         </is>
       </c>
       <c r="E177" s="4" t="n">
@@ -5028,21 +5040,25 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>8809239803596</t>
+        </is>
+      </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F178" s="5" t="n"/>
       <c r="G178" s="5" t="n"/>
@@ -5051,7 +5067,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -5060,16 +5076,16 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>8809239803596</t>
+          <t>8809239803589</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
         </is>
       </c>
       <c r="E179" s="4" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F179" s="5" t="n"/>
       <c r="G179" s="5" t="n"/>
@@ -5078,7 +5094,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -5087,16 +5103,16 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>8809239803589</t>
+          <t>8809508850498</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
+          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F180" s="5" t="n"/>
       <c r="G180" s="5" t="n"/>
@@ -5104,88 +5120,88 @@
       <c r="I180" s="5" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" t="n">
-        <v>164</v>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>8809508850498</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F181" s="5" t="n"/>
-      <c r="G181" s="5" t="n"/>
-      <c r="H181" s="5" t="n"/>
-      <c r="I181" s="5" t="n"/>
+      <c r="A181" s="2" t="n"/>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>PRRETI</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" s="3" t="n"/>
+      <c r="F181" s="2" t="n"/>
+      <c r="G181" s="2" t="n"/>
+      <c r="H181" s="2" t="n"/>
+      <c r="I181" s="2" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n"/>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="A182" t="n">
+        <v>165</v>
+      </c>
+      <c r="B182" t="inlineStr">
         <is>
           <t>PRRETI</t>
         </is>
       </c>
-      <c r="C182" s="2" t="n"/>
-      <c r="D182" s="2" t="n"/>
-      <c r="E182" s="3" t="n"/>
-      <c r="F182" s="2" t="n"/>
-      <c r="G182" s="2" t="n"/>
-      <c r="H182" s="2" t="n"/>
-      <c r="I182" s="2" t="n"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>PRRETI Honey&amp;Berry Lip Sleeping Mask 15 гр</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F182" s="5" t="n"/>
+      <c r="G182" s="5" t="n"/>
+      <c r="H182" s="5" t="n"/>
+      <c r="I182" s="5" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" t="n">
-        <v>165</v>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>PRRETI</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>PRRETI Honey&amp;Berry Lip Sleeping Mask 15 гр</t>
-        </is>
-      </c>
-      <c r="E183" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F183" s="5" t="n"/>
-      <c r="G183" s="5" t="n"/>
-      <c r="H183" s="5" t="n"/>
-      <c r="I183" s="5" t="n"/>
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" s="3" t="n"/>
+      <c r="F183" s="2" t="n"/>
+      <c r="G183" s="2" t="n"/>
+      <c r="H183" s="2" t="n"/>
+      <c r="I183" s="2" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n"/>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="A184" t="n">
+        <v>166</v>
+      </c>
+      <c r="B184" t="inlineStr">
         <is>
           <t>ROUND LAB</t>
         </is>
       </c>
-      <c r="C184" s="2" t="n"/>
-      <c r="D184" s="2" t="n"/>
-      <c r="E184" s="3" t="n"/>
-      <c r="F184" s="2" t="n"/>
-      <c r="G184" s="2" t="n"/>
-      <c r="H184" s="2" t="n"/>
-      <c r="I184" s="2" t="n"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>8809738599044</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>1025 DOKDO BUBBLE FOAM_150ml</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F184" s="5" t="n"/>
+      <c r="G184" s="5" t="n"/>
+      <c r="H184" s="5" t="n"/>
+      <c r="I184" s="5" t="n"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -5194,16 +5210,16 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>8809738599044</t>
+          <t>8809849802408</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1025 DOKDO BUBBLE FOAM_150ml</t>
+          <t>PINE CALMING CICA BODY WASH_400ml</t>
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F185" s="5" t="n"/>
       <c r="G185" s="5" t="n"/>
@@ -5212,7 +5228,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -5221,16 +5237,16 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>8809849802408</t>
+          <t>8809864754126</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>PINE CALMING CICA BODY WASH_400ml</t>
+          <t>PINE CALMING CICA CLEANSER_150ml</t>
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F186" s="5" t="n"/>
       <c r="G186" s="5" t="n"/>
@@ -5239,7 +5255,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -5248,16 +5264,16 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>8809864754126</t>
+          <t>8809962542137</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>PINE CALMING CICA CLEANSER_150ml</t>
+          <t>PINE CALMING CICA CREAM PLUS_60ml</t>
         </is>
       </c>
       <c r="E187" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F187" s="5" t="n"/>
       <c r="G187" s="5" t="n"/>
@@ -5266,7 +5282,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -5275,16 +5291,16 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>8809962542137</t>
+          <t>8809750462708</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>PINE CALMING CICA CREAM PLUS_60ml</t>
+          <t>PINE CALMING CICA PAD_50pcs</t>
         </is>
       </c>
       <c r="E188" s="4" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F188" s="5" t="n"/>
       <c r="G188" s="5" t="n"/>
@@ -5293,7 +5309,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -5302,16 +5318,16 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>8809750462708</t>
+          <t>8809738608364</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>PINE CALMING CICA PAD_50pcs</t>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
         </is>
       </c>
       <c r="E189" s="4" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F189" s="5" t="n"/>
       <c r="G189" s="5" t="n"/>
@@ -5320,7 +5336,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -5329,16 +5345,16 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>8809738608364</t>
+          <t>8809657114731</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F190" s="5" t="n"/>
       <c r="G190" s="5" t="n"/>
@@ -5347,7 +5363,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -5356,16 +5372,16 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>8809657114731</t>
+          <t>8809738600221</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F191" s="5" t="n"/>
       <c r="G191" s="5" t="n"/>
@@ -5374,7 +5390,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -5383,12 +5399,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>8809738600221</t>
+          <t>8809962541840</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
+          <t>ROUND LAB CAMELLIA DEEP COLLAGEN FIRMING CREAM_50ml</t>
         </is>
       </c>
       <c r="E192" s="4" t="n">
@@ -5401,7 +5417,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -5410,16 +5426,16 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>8809962541840</t>
+          <t>8809738593080</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ROUND LAB CAMELLIA DEEP COLLAGEN FIRMING CREAM_50ml</t>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
         </is>
       </c>
       <c r="E193" s="4" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F193" s="5" t="n"/>
       <c r="G193" s="5" t="n"/>
@@ -5428,7 +5444,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -5437,16 +5453,16 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>8809738593080</t>
+          <t>8809783325667</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F194" s="5" t="n"/>
       <c r="G194" s="5" t="n"/>
@@ -5455,7 +5471,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -5464,16 +5480,16 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>8809783325667</t>
+          <t>8809962540553</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
+          <t>ROUND LAB STICK POUCH KIT</t>
         </is>
       </c>
       <c r="E195" s="4" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F195" s="5" t="n"/>
       <c r="G195" s="5" t="n"/>
@@ -5482,7 +5498,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -5491,16 +5507,16 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>8809962540553</t>
+          <t>8809738593240</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ROUND LAB STICK POUCH KIT</t>
+          <t>SOYBEAN SERUM_50ml</t>
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F196" s="5" t="n"/>
       <c r="G196" s="5" t="n"/>
@@ -5508,50 +5524,50 @@
       <c r="I196" s="5" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" t="n">
-        <v>178</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>8809738593240</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>SOYBEAN SERUM_50ml</t>
-        </is>
-      </c>
-      <c r="E197" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F197" s="5" t="n"/>
-      <c r="G197" s="5" t="n"/>
-      <c r="H197" s="5" t="n"/>
-      <c r="I197" s="5" t="n"/>
+      <c r="A197" s="2" t="n"/>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n"/>
+      <c r="D197" s="2" t="n"/>
+      <c r="E197" s="3" t="n"/>
+      <c r="F197" s="2" t="n"/>
+      <c r="G197" s="2" t="n"/>
+      <c r="H197" s="2" t="n"/>
+      <c r="I197" s="2" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n"/>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="A198" t="n">
+        <v>179</v>
+      </c>
+      <c r="B198" t="inlineStr">
         <is>
           <t>SKIN1004</t>
         </is>
       </c>
-      <c r="C198" s="2" t="n"/>
-      <c r="D198" s="2" t="n"/>
-      <c r="E198" s="3" t="n"/>
-      <c r="F198" s="2" t="n"/>
-      <c r="G198" s="2" t="n"/>
-      <c r="H198" s="2" t="n"/>
-      <c r="I198" s="2" t="n"/>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>8809576260601</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F198" s="5" t="n"/>
+      <c r="G198" s="5" t="n"/>
+      <c r="H198" s="5" t="n"/>
+      <c r="I198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -5560,12 +5576,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>8809576260601</t>
+          <t>8809576261134</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
+          <t>SKIN1004 Madagascar Centella Soothing Cream 75ml</t>
         </is>
       </c>
       <c r="E199" s="4" t="n">
@@ -5578,7 +5594,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -5587,12 +5603,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>8809576261134</t>
+          <t>8809576261172</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>SKIN1004 Madagascar Centella Soothing Cream 75ml</t>
+          <t>SKIN1004 Madagascar Centella Tone Brightening Capsule Ampoule 100ml</t>
         </is>
       </c>
       <c r="E200" s="4" t="n">
@@ -5604,144 +5620,144 @@
       <c r="I200" s="5" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" t="n">
-        <v>181</v>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>SKIN1004</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>8809576261172</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>SKIN1004 Madagascar Centella Tone Brightening Capsule Ampoule 100ml</t>
-        </is>
-      </c>
-      <c r="E201" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F201" s="5" t="n"/>
-      <c r="G201" s="5" t="n"/>
-      <c r="H201" s="5" t="n"/>
-      <c r="I201" s="5" t="n"/>
+      <c r="A201" s="2" t="n"/>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="n"/>
+      <c r="D201" s="2" t="n"/>
+      <c r="E201" s="3" t="n"/>
+      <c r="F201" s="2" t="n"/>
+      <c r="G201" s="2" t="n"/>
+      <c r="H201" s="2" t="n"/>
+      <c r="I201" s="2" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n"/>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="A202" t="n">
+        <v>182</v>
+      </c>
+      <c r="B202" t="inlineStr">
         <is>
           <t>SOME BY MI</t>
         </is>
       </c>
-      <c r="C202" s="2" t="n"/>
-      <c r="D202" s="2" t="n"/>
-      <c r="E202" s="3" t="n"/>
-      <c r="F202" s="2" t="n"/>
-      <c r="G202" s="2" t="n"/>
-      <c r="H202" s="2" t="n"/>
-      <c r="I202" s="2" t="n"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>8809326334224</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
+        </is>
+      </c>
+      <c r="E202" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F202" s="5" t="n"/>
+      <c r="G202" s="5" t="n"/>
+      <c r="H202" s="5" t="n"/>
+      <c r="I202" s="5" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" t="n">
-        <v>182</v>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>SOME BY MI</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>8809326334224</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
-        </is>
-      </c>
-      <c r="E203" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F203" s="5" t="n"/>
-      <c r="G203" s="5" t="n"/>
-      <c r="H203" s="5" t="n"/>
-      <c r="I203" s="5" t="n"/>
+      <c r="A203" s="2" t="n"/>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>THE ORDINARY</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n"/>
+      <c r="D203" s="2" t="n"/>
+      <c r="E203" s="3" t="n"/>
+      <c r="F203" s="2" t="n"/>
+      <c r="G203" s="2" t="n"/>
+      <c r="H203" s="2" t="n"/>
+      <c r="I203" s="2" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n"/>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="A204" t="n">
+        <v>183</v>
+      </c>
+      <c r="B204" t="inlineStr">
         <is>
           <t>THE ORDINARY</t>
         </is>
       </c>
-      <c r="C204" s="2" t="n"/>
-      <c r="D204" s="2" t="n"/>
-      <c r="E204" s="3" t="n"/>
-      <c r="F204" s="2" t="n"/>
-      <c r="G204" s="2" t="n"/>
-      <c r="H204" s="2" t="n"/>
-      <c r="I204" s="2" t="n"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
+        </is>
+      </c>
+      <c r="E204" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F204" s="5" t="n"/>
+      <c r="G204" s="5" t="n"/>
+      <c r="H204" s="5" t="n"/>
+      <c r="I204" s="5" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" t="n">
-        <v>183</v>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>THE ORDINARY</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
-        </is>
-      </c>
-      <c r="E205" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="F205" s="5" t="n"/>
-      <c r="G205" s="5" t="n"/>
-      <c r="H205" s="5" t="n"/>
-      <c r="I205" s="5" t="n"/>
+      <c r="A205" s="2" t="n"/>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="n"/>
+      <c r="D205" s="2" t="n"/>
+      <c r="E205" s="3" t="n"/>
+      <c r="F205" s="2" t="n"/>
+      <c r="G205" s="2" t="n"/>
+      <c r="H205" s="2" t="n"/>
+      <c r="I205" s="2" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n"/>
-      <c r="B206" s="2" t="inlineStr">
+      <c r="A206" t="n">
+        <v>184</v>
+      </c>
+      <c r="B206" t="inlineStr">
         <is>
           <t>VT COSMETICS</t>
         </is>
       </c>
-      <c r="C206" s="2" t="n"/>
-      <c r="D206" s="2" t="n"/>
-      <c r="E206" s="3" t="n"/>
-      <c r="F206" s="2" t="n"/>
-      <c r="G206" s="2" t="n"/>
-      <c r="H206" s="2" t="n"/>
-      <c r="I206" s="2" t="n"/>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F206" s="5" t="n"/>
+      <c r="G206" s="5" t="n"/>
+      <c r="H206" s="5" t="n"/>
+      <c r="I206" s="5" t="n"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>VT COSMETICS</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>8803463006501</t>
+        </is>
+      </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+          <t>VT REEDLE S LIP PLUMPER EXPERT</t>
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F207" s="5" t="n"/>
       <c r="G207" s="5" t="n"/>
@@ -5750,25 +5766,21 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>VT COSMETICS</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>8803463006501</t>
-        </is>
-      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VT REEDLE S LIP PLUMPER EXPERT</t>
+          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F208" s="5" t="n"/>
       <c r="G208" s="5" t="n"/>
@@ -5776,48 +5788,25 @@
       <c r="I208" s="5" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" t="n">
-        <v>186</v>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
-        </is>
-      </c>
-      <c r="E209" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="F209" s="5" t="n"/>
-      <c r="G209" s="5" t="n"/>
-      <c r="H209" s="5" t="n"/>
-      <c r="I209" s="5" t="n"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="6" t="n"/>
-      <c r="B210" s="6" t="inlineStr">
+      <c r="A209" s="6" t="n"/>
+      <c r="B209" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C210" s="6" t="n"/>
-      <c r="D210" s="6" t="inlineStr">
+      <c r="C209" s="6" t="n"/>
+      <c r="D209" s="6" t="inlineStr">
         <is>
           <t>позиций: 186</t>
         </is>
       </c>
-      <c r="E210" s="7" t="n">
+      <c r="E209" s="7" t="n">
         <v>66900</v>
       </c>
-      <c r="F210" s="6" t="n"/>
-      <c r="G210" s="6" t="n"/>
-      <c r="H210" s="6" t="n"/>
-      <c r="I210" s="6" t="n"/>
+      <c r="F209" s="6" t="n"/>
+      <c r="G209" s="6" t="n"/>
+      <c r="H209" s="6" t="n"/>
+      <c r="I209" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5830,7 +5819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5914,10 +5903,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11100</v>
+        <v>11300</v>
       </c>
     </row>
     <row r="7">
@@ -6040,72 +6029,72 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NOUGH</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>200</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>PRRETI</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>7000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PRRETI</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>200</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>SKIN1004</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>SOME BY MI</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOME BY MI</t>
+          <t>THE ORDINARY</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6118,39 +6107,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>THE ORDINARY</t>
+          <t>VT COSMETICS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>200</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>VT COSMETICS</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>ВСЕГО</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B23" s="6" t="n">
         <v>186</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C23" s="7" t="n">
         <v>66900</v>
       </c>
     </row>
